--- a/sources/xlsx/Agents.xlsx
+++ b/sources/xlsx/Agents.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9060" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7710" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="agents" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="map" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RDF-Relations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="relations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RDF-Relations" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -84,13 +85,21 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="001F4E79"/>
+      <color rgb="FF1F4E79"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -102,17 +111,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FB"/>
+        <fgColor rgb="FFEBF3FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,26 +135,26 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -157,9 +166,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -169,9 +176,14 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -593,9 +605,9 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16.44140625" customWidth="1" style="14" min="1" max="1"/>
-    <col width="19.109375" customWidth="1" style="14" min="2" max="2"/>
-    <col width="121.109375" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="16.44140625" customWidth="1" style="15" min="1" max="1"/>
+    <col width="19.109375" customWidth="1" style="15" min="2" max="2"/>
+    <col width="121.109375" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,128 +618,128 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="3" t="n">
         <v>20260512</v>
       </c>
-      <c r="C3" s="6" t="n"/>
+      <c r="C3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Modified</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="3" t="n">
         <v>20260512</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="3" t="n">
         <v>20260512</v>
       </c>
-      <c r="C5" s="6" t="n"/>
+      <c r="C5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Ongoing*</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Primary Contact</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Ben Norton</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
+      <c r="C9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n"/>
+      <c r="C10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>ben.norton@yale.edu</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
+      <c r="C11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Concept Scheme Annotation Properties</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1LFrSqBu77SraEJN6zpjMvn6MF8rIcOnQIMt-_8LxTA4/edit?gid=1334808172#gid=1334808172</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Concept Annotation Properties</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1LFrSqBu77SraEJN6zpjMvn6MF8rIcOnQIMt-_8LxTA4/edit?gid=1986942826#gid=1986942826</t>
         </is>
@@ -762,122 +774,128 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="40" customWidth="1" style="12" min="1" max="1"/>
-    <col width="28" customWidth="1" style="12" min="2" max="3"/>
-    <col width="22" customWidth="1" style="12" min="4" max="4"/>
-    <col width="36" bestFit="1" customWidth="1" style="12" min="5" max="5"/>
-    <col width="18.88671875" bestFit="1" customWidth="1" style="12" min="6" max="6"/>
-    <col width="41.77734375" customWidth="1" style="12" min="7" max="7"/>
-    <col width="42.6640625" customWidth="1" style="12" min="8" max="8"/>
-    <col width="8.33203125" bestFit="1" customWidth="1" style="12" min="9" max="9"/>
-    <col width="37.5546875" bestFit="1" customWidth="1" style="12" min="10" max="10"/>
-    <col width="32" customWidth="1" style="12" min="11" max="11"/>
-    <col width="22" customWidth="1" style="12" min="12" max="12"/>
-    <col width="36.21875" bestFit="1" customWidth="1" style="12" min="13" max="13"/>
-    <col width="30" customWidth="1" style="12" min="14" max="14"/>
-    <col width="113" bestFit="1" customWidth="1" style="12" min="15" max="15"/>
-    <col width="8.88671875" customWidth="1" style="12" min="16" max="16384"/>
+    <col width="40" customWidth="1" style="17" min="1" max="1"/>
+    <col width="28" customWidth="1" style="17" min="2" max="3"/>
+    <col width="22" customWidth="1" style="17" min="4" max="4"/>
+    <col width="36" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
+    <col width="18.88671875" bestFit="1" customWidth="1" style="17" min="6" max="6"/>
+    <col width="32.5546875" customWidth="1" style="17" min="7" max="7"/>
+    <col width="29" customWidth="1" style="17" min="8" max="8"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" style="17" min="9" max="9"/>
+    <col width="37.5546875" bestFit="1" customWidth="1" style="17" min="10" max="10"/>
+    <col width="32" customWidth="1" style="17" min="11" max="11"/>
+    <col width="22" customWidth="1" style="17" min="12" max="12"/>
+    <col width="36.21875" bestFit="1" customWidth="1" style="17" min="13" max="13"/>
+    <col width="30" customWidth="1" style="17" min="14" max="14"/>
+    <col width="113" bestFit="1" customWidth="1" style="17" min="15" max="15"/>
+    <col width="8.88671875" customWidth="1" style="17" min="16" max="16"/>
+    <col width="8.88671875" customWidth="1" style="17" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>agentURI</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>blankNodeLabel</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>agentName</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>agentType</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>orcidURI</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>agentEmail</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>agentURL</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>agentHomepage</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>acronym</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>memberOfURI</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="17" t="inlineStr">
         <is>
           <t>memberOfName</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="17" t="inlineStr">
         <is>
           <t>memberOfRole</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="17" t="inlineStr">
         <is>
           <t>parentOrgURI</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="17" t="inlineStr">
         <is>
           <t>parentOrgName</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="17" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="14">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>agent_ben_norton</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Ben Norton</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>schema:Person</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>https://orcid.org/0000-0002-5819-9134</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>ben.norton@yale.edu</t>
         </is>
@@ -887,153 +905,153 @@
           <t>https://mbnorton.com</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>Mineralogy Extension Task Group</t>
         </is>
       </c>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>co-convener</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="M2" s="17" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/yale-university</t>
         </is>
       </c>
-      <c r="N2" s="12" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="14">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="15">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>agent_mineralogy_extension_task_group</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Mineralogy Extension Task Group</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>schema:Organization</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>https://www.tdwg.org/community/esp/mineralogy/</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>https://www.tdwg.org/community/esp/mineralogy/</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>MinExt</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/tdwg</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Biodiversity Information Standards</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="14">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="15">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/tdwg</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>agent_biodiversity_information_standards</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Biodiversity Information Standards</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>schema:Organization</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>https://www.tdwg.org</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>https://www.tdwg.org</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>TDWG</t>
         </is>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t>Taxonomic Databases Working Group, now Biodiversity Information Standards</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="14">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="15">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/yale-university</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>agent_yale_university</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>schema:Organization</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>https://www.yale.edu</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>https://www.yale.edu</t>
         </is>
       </c>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="O5" s="17" t="inlineStr">
         <is>
           <t>Also identified by GBIF GRSciColl IRI: https://scientific-collections.gbif.org/institution/75f50140-830d-4630-a290-3d6e951a7c29</t>
         </is>
@@ -1056,371 +1074,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="45.109375" customWidth="1" style="14" min="1" max="1"/>
-    <col width="61.109375" customWidth="1" style="14" min="2" max="2"/>
+    <col width="37.33203125" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
+    <col width="40.109375" bestFit="1" customWidth="1" style="15" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="14.4" customHeight="1" s="15">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>agentURI</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>resourceURI</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>hadRole</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>relatedAgentURI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>agentRole</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.4" customHeight="1" s="15">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/hazard-type</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:publisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/yale-university</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>https://d-nb.info/standards/elementset/agrelon#hasEmployer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.4" customHeight="1" s="15">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/tdwg</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>https://www.w3.org/ns/org#unitOf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1" s="15">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/hazard-type</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:author</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/hazard-type</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:editor</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/hazard-type</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:custodian</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/aggregate-form</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:publisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/aggregate-form</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:author</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/aggregate-form</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:editor</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/aggregate-form</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:custodian</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/constituent-part-proportion</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:publisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/constituent-part-proportion</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:author</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/constituent-part-proportion</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:editor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/constituent-part-proportion</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:custodian</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:publisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:author</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:editor</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:custodian</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:publisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/ben-norton</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:author</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:editor</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>isoroles:custodian</t>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>https://d-nb.info/standards/elementset/agrelon#isMemberOf</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1431,200 +1168,617 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="54" customWidth="1" style="14" min="1" max="1"/>
-    <col width="54" customWidth="1" style="14" min="2" max="2"/>
-    <col width="44" customWidth="1" style="14" min="3" max="3"/>
+    <col width="45.109375" customWidth="1" style="15" min="1" max="1"/>
+    <col width="61.109375" customWidth="1" style="15" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="14">
-      <c r="A1" s="15" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>agentURI</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resourceURI</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>hadRole</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="14">
-      <c r="A2" s="16" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/hazard-type</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/hazard-type</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:author</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/hazard-type</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/hazard-type</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:custodian</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/aggregate-form</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/aggregate-form</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:author</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/aggregate-form</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/aggregate-form</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:custodian</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/constituent-part-proportion</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/constituent-part-proportion</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:author</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/constituent-part-proportion</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/constituent-part-proportion</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:custodian</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:author</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-material-type</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:custodian</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:author</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/geological-specimen-name-type</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>isoroles:custodian</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="54" customWidth="1" style="15" min="1" max="2"/>
+    <col width="44" customWidth="1" style="15" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.95" customHeight="1" s="15">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>agentURI</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>resourceURI</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>hadRole</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.05" customHeight="1" s="15">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/ben-norton</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>https://kos.resources.org/def/aggregate-form</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>isoroles:editor, isoroles:publisher</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="14">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="3" ht="16.05" customHeight="1" s="15">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/constituent-part-proportion</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>isoroles:editor, isoroles:publisher</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="14">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="16.05" customHeight="1" s="15">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/geological-specimen-material-type</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>isoroles:editor, isoroles:publisher</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="14">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="5" ht="16.05" customHeight="1" s="15">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/geological-specimen-name-type</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>isoroles:editor, isoroles:publisher</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="14">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="16.05" customHeight="1" s="15">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>https://kos.geospecimens.org/org/ben-norton</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/hazard-type</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>isoroles:editor, isoroles:publisher</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="14">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="7" ht="16.05" customHeight="1" s="15">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/aggregate-form</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>isoroles:contributor, isoroles:custodian</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="14">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="8" ht="16.05" customHeight="1" s="15">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/constituent-part-proportion</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>isoroles:contributor, isoroles:custodian</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="14">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="9" ht="16.05" customHeight="1" s="15">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/geological-specimen-material-type</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>isoroles:contributor, isoroles:custodian</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="14">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="10" ht="16.05" customHeight="1" s="15">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/geological-specimen-name-type</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>isoroles:contributor, isoroles:custodian</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="14">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>https://kos.geospecimens.org/org/minext</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="11" ht="16.05" customHeight="1" s="15">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>https://kos.geospecimens.org/org/minext</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>https://kos.resources.org/def/hazard-type</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>isoroles:contributor, isoroles:custodian</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>https://www.w3.org/ns/org#unitOf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>https://www.w3.org/ns/org#memberOf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>https://www.w3.org/ns/org#hasMember</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>https://d-nb.info/standards/elementset/agrelon#hasEmployer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sources/xlsx/Agents.xlsx
+++ b/sources/xlsx/Agents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\repos\vocabularies\vocab-processor\sources\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E251279-53C6-4882-B228-9C1512529FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F40CF-C8B8-43BD-9218-CEFA46F64361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7710" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3072" yWindow="3072" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="78">
   <si>
     <t>agentURI</t>
   </si>
@@ -278,9 +278,6 @@
     <t>https://www.w3.org/ns/org#hasMember</t>
   </si>
   <si>
-    <t>https://kos.geospecimens.org/vocab/geological-material-assertion-types</t>
-  </si>
-  <si>
     <t>https://kos.geospecimens.org/def/kos-meta</t>
   </si>
   <si>
@@ -293,16 +290,16 @@
     <t>https://kos.geospecimens.org/def/constituent-part-proportion</t>
   </si>
   <si>
-    <t>https://kos.geospecimens.org/def/geological-specimen-material-type</t>
-  </si>
-  <si>
     <t>https://kos.geospecimens.org/def/geological-specimen-name-type</t>
   </si>
   <si>
     <t>https://kos.geospecimens.org/def/geological-specimen-material-category</t>
   </si>
   <si>
-    <t>http://kos.geospecimens.org/def/luster</t>
+    <t>https://kos.geospecimens.org/def/luster</t>
+  </si>
+  <si>
+    <t>https://kos.geospecimens.org/def/geological-material-assertion-type</t>
   </si>
 </sst>
 </file>
@@ -312,7 +309,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,17 +370,6 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -392,30 +378,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -423,27 +394,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -457,20 +413,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -922,19 +869,19 @@
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="16"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="10" t="s">
         <v>53</v>
       </c>
@@ -962,184 +909,184 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="28" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32" style="1" customWidth="1"/>
-    <col min="12" max="12" width="22" style="1" customWidth="1"/>
-    <col min="13" max="13" width="36.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="113" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="8.88671875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="44" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="45.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="113" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="8.88671875" style="14" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1176,10 +1123,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1187,21 +1134,21 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1227,359 +1174,359 @@
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="61.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="76.33203125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C6" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C7" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C8" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C9" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C10" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C11" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C12" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C13" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="18" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C18" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="18" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C19" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="18" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C20" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="18" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C21" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="17" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C22" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="17" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C23" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="17" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C24" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="17" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C25" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="18" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C29" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="18" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C30" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="18" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C31" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="18" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="14" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1589,6 +1536,14 @@
     <hyperlink ref="B27" r:id="rId2" xr:uid="{5C181E0D-3F4C-45D5-80BD-7724CDA5BAE6}"/>
     <hyperlink ref="B28" r:id="rId3" xr:uid="{18E8852A-D42A-41CE-ADDC-6D03BD6E6E2B}"/>
     <hyperlink ref="B14:B17" r:id="rId4" display="https://kos.geospecimens.org/def/geological-specimen-material-category" xr:uid="{F53FBDE5-5425-424E-9E82-873A55B0BCD9}"/>
+    <hyperlink ref="B22" r:id="rId5" xr:uid="{1E63138F-9297-46F9-A66C-C6039413EA75}"/>
+    <hyperlink ref="B23" r:id="rId6" xr:uid="{03C41D90-6648-4BC3-AFCA-FA0DFFD68052}"/>
+    <hyperlink ref="B24" r:id="rId7" xr:uid="{785B6ABF-37B7-4FA3-8151-010649E9C054}"/>
+    <hyperlink ref="B25" r:id="rId8" xr:uid="{7B50CC0B-095B-42D0-A88F-84FC9E6AF603}"/>
+    <hyperlink ref="B29" r:id="rId9" xr:uid="{1803FF82-DB0E-403A-9E27-B53B69C04AA1}"/>
+    <hyperlink ref="B30" r:id="rId10" xr:uid="{B128C2BA-739F-4818-ADEB-6C3621FAE7E6}"/>
+    <hyperlink ref="B31" r:id="rId11" xr:uid="{A7E1F2DC-50A5-4AC8-89C6-A3516A18FDC5}"/>
+    <hyperlink ref="B32" r:id="rId12" xr:uid="{D069583E-B0C3-4A40-B0A6-3ED71F91659E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1596,162 +1551,187 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="54" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="60.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="13" t="s">
+    <row r="5" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="12" t="s">
+    <row r="8" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="12" t="s">
+    <row r="13" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C13" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="13" t="s">
+    <row r="14" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -1759,7 +1739,22 @@
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
     </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{5C3B633F-53D2-4AC8-AB6B-C3DB42A78881}"/>
+    <hyperlink ref="B12" r:id="rId2" xr:uid="{876D9DAA-0E4A-43C9-835B-101D79FFFCD2}"/>
+    <hyperlink ref="B11" r:id="rId3" xr:uid="{C1E724E7-0F14-49C6-9A76-7DDC1A99B318}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{BAA45C28-2E56-4F7F-AC40-16EF1AEFA9C8}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>